--- a/Knockouts/Ladies.xlsx
+++ b/Knockouts/Ladies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\Knockouts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09495A24-BAA3-49E0-8AD9-8114829EA146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5947CB-D4A6-45EF-85F1-07C29868471B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="585" yWindow="345" windowWidth="20370" windowHeight="10905" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
   <sheets>
     <sheet name="Knockout Matches" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>Match</t>
   </si>
@@ -97,12 +97,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>G1W</t>
-  </si>
-  <si>
-    <t>G2W</t>
-  </si>
-  <si>
     <t>RAVENS TTC SENIER TOURNAMENT 2026</t>
   </si>
   <si>
@@ -115,12 +109,6 @@
     <t>LADIES OPEN</t>
   </si>
   <si>
-    <t>G2R</t>
-  </si>
-  <si>
-    <t>G1R</t>
-  </si>
-  <si>
     <t>Saturday</t>
   </si>
   <si>
@@ -134,6 +122,30 @@
   </si>
   <si>
     <t>Table</t>
+  </si>
+  <si>
+    <t>Musfiquh Kalam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boundary </t>
+  </si>
+  <si>
+    <t>Angeline Wood</t>
+  </si>
+  <si>
+    <t>Ravens</t>
+  </si>
+  <si>
+    <t>Janine Sait</t>
+  </si>
+  <si>
+    <t>Community House</t>
+  </si>
+  <si>
+    <t>Tazmin Haris</t>
+  </si>
+  <si>
+    <t>Duinefontein TTC</t>
   </si>
 </sst>
 </file>
@@ -688,16 +700,16 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="M1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -712,26 +724,26 @@
       </c>
       <c r="D2" t="str" cm="1">
         <f t="array" ref="D2:F2">'Knockout Grid'!A6:C6</f>
-        <v>G1W</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
+        <v>Musfiquh Kalam</v>
+      </c>
+      <c r="E2" t="str">
+        <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" t="str" cm="1">
         <f t="array" ref="G2:I2">'Knockout Grid'!A7:C7</f>
-        <v>G2R</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
+        <v>Tazmin Haris</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Duinefontein TTC</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K2" s="13">
         <v>46172</v>
@@ -755,26 +767,26 @@
       </c>
       <c r="D3" t="str" cm="1">
         <f t="array" ref="D3:F3">'Knockout Grid'!A38:C38</f>
-        <v>G1R</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
+        <v>Angeline Wood</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Ravens</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" t="str" cm="1">
         <f t="array" ref="G3:I3">'Knockout Grid'!A39:C39</f>
-        <v>G2W</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
+        <v>Janine Sait</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Community House</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K3" s="13">
         <v>46172</v>
@@ -817,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K4" s="13">
         <v>46172</v>
@@ -850,7 +862,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="34.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -877,7 +889,7 @@
     </row>
     <row r="2" spans="1:23" ht="34.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -904,21 +916,21 @@
     </row>
     <row r="3" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
     </row>
     <row r="4" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B4" s="13">
         <v>46172</v>
@@ -947,17 +959,21 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="10"/>
+        <v>20</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="C6" s="11"/>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>27</v>
+      </c>
       <c r="C7" s="11"/>
       <c r="D7" s="1"/>
     </row>
@@ -1001,7 +1017,7 @@
     <row r="20" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D20" s="3"/>
       <c r="F20" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G20" s="13">
         <v>46172</v>
@@ -1077,7 +1093,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B36" s="13">
         <v>46172</v>
@@ -1103,17 +1119,21 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B38" s="10"/>
+        <v>22</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>23</v>
+      </c>
       <c r="C38" s="11"/>
       <c r="D38" s="4"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="10"/>
+        <v>24</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>25</v>
+      </c>
       <c r="C39" s="11"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">

--- a/Knockouts/Ladies.xlsx
+++ b/Knockouts/Ladies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5947CB-D4A6-45EF-85F1-07C29868471B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C8015B-1390-42DB-A046-8AC66CFA85A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="28">
   <si>
     <t>Match</t>
   </si>
@@ -730,7 +730,7 @@
         <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2" t="str" cm="1">
         <f t="array" ref="G2:I2">'Knockout Grid'!A7:C7</f>
@@ -773,7 +773,7 @@
         <v>Ravens</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="str" cm="1">
         <f t="array" ref="G3:I3">'Knockout Grid'!A39:C39</f>
@@ -808,22 +808,22 @@
       <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" cm="1">
+      <c r="D4" t="str" cm="1">
         <f t="array" ref="D4:F4">'Knockout Grid'!F22:H22</f>
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
+        <v>Musfiquh Kalam</v>
+      </c>
+      <c r="E4" t="str">
+        <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" cm="1">
+      <c r="G4" t="str" cm="1">
         <f t="array" ref="G4:I4">'Knockout Grid'!F23:H23</f>
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
+        <v>Angeline Wood</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Ravens</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -964,7 +964,9 @@
       <c r="B6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="11"/>
+      <c r="C6" s="11">
+        <v>3</v>
+      </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
@@ -974,7 +976,9 @@
       <c r="B7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="11"/>
+      <c r="C7" s="11">
+        <v>0</v>
+      </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -1044,14 +1048,22 @@
     <row r="22" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D22" s="3"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="10"/>
+      <c r="F22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="H22" s="11"/>
     </row>
     <row r="23" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D23" s="3"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="10"/>
+      <c r="F23" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>23</v>
+      </c>
       <c r="H23" s="11"/>
     </row>
     <row r="24" spans="4:9" x14ac:dyDescent="0.25">
@@ -1124,7 +1136,9 @@
       <c r="B38" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="11"/>
+      <c r="C38" s="11">
+        <v>3</v>
+      </c>
       <c r="D38" s="4"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1134,7 +1148,9 @@
       <c r="B39" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="11"/>
+      <c r="C39" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B40" s="5"/>

--- a/Knockouts/Ladies.xlsx
+++ b/Knockouts/Ladies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Ravens Seniors\Knockouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C8015B-1390-42DB-A046-8AC66CFA85A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB27518-87CC-44D2-BD74-658AD3545044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{6F46E828-8FFD-4531-838C-1A16471CA10A}"/>
   </bookViews>
@@ -816,7 +816,7 @@
         <v xml:space="preserve">Boundary </v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="str" cm="1">
         <f t="array" ref="G4:I4">'Knockout Grid'!F23:H23</f>
@@ -1054,7 +1054,9 @@
       <c r="G22" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="11"/>
+      <c r="H22" s="11">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D23" s="3"/>
@@ -1064,7 +1066,9 @@
       <c r="G23" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="11"/>
+      <c r="H23" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D24" s="3"/>
